--- a/reports/二级子公司D_利润表_2025-11.xlsx
+++ b/reports/二级子公司D_利润表_2025-11.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>80209458</v>
+        <v>82380447</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>78419242</v>
+        <v>78842461</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>903427703</v>
+        <v>902930691</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>270877</v>
+        <v>273175</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>3115794</v>
+        <v>3118793</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>233800</v>
+        <v>233884</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>2672120</v>
+        <v>2674080</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>192945</v>
+        <v>194523</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>2224989</v>
+        <v>2228666</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>175643</v>
+        <v>174645</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>2004430</v>
+        <v>2005616</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>96435</v>
+        <v>96784</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>1112426</v>
+        <v>1113914</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>77990</v>
+        <v>77265</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>890807</v>
+        <v>890747</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>79161768</v>
+        <v>81330171</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>77371552</v>
+        <v>77792185</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>4365569</v>
+        <v>4342009</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>50083545</v>
+        <v>50036710</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>338783</v>
+        <v>338269</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>3894935</v>
+        <v>3890939</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>584243</v>
+        <v>581217</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>6680023</v>
+        <v>6670178</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>69479547</v>
+        <v>69921832</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>801018210</v>
+        <v>800585993</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1170849</v>
+        <v>1168053</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>13362702</v>
+        <v>13348114</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>385695</v>
+        <v>390010</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>4449684</v>
+        <v>4451505</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>1950331</v>
+        <v>1951574</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>22270682</v>
+        <v>22268636</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>483008</v>
+        <v>487766</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>5562857</v>
+        <v>5569555</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>1750235</v>
+        <v>1753744</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>20038948</v>
+        <v>20056142</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>39981</v>
+        <v>40096</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>439961</v>
+        <v>440583</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>1047516</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>12033367</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>696630</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>8019773</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>52629344</v>
+        <v>56373860</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>47158740</v>
+        <v>47151660</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>46280873</v>
+        <v>46283110</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>533961688</v>
+        <v>533895091</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>877867</v>
+        <v>868550</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>10021989</v>
+        <v>10006959</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>1740150</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>20010298</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>558153</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>6403471</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>349724</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>4003096</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>420612</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>4805606</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>315959</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>3605963</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>210776</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>2405166</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>175576</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>2005137</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>819562</v>
+        <v>827964</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>9455614</v>
+        <v>9471183</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>634137</v>
+        <v>631808</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>7238196</v>
+        <v>7243133</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>482626</v>
+        <v>484798</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>5562510</v>
+        <v>5570832</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>3698778</v>
+        <v>3675548</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>42308091</v>
+        <v>42324348</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>149753</v>
+        <v>144808</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>1649691</v>
+        <v>1669934</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>319885</v>
+        <v>318132</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>3520026</v>
+        <v>3518867</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>360837</v>
+        <v>318132</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>3960685</v>
+        <v>3518867</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>39839</v>
+        <v>39804</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>439853</v>
+        <v>439485</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>161503</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>1779641</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>305342</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>3501968</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>108197</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>1186889</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>81325</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>890583</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>135741</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>1485122</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>439119</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>5011068</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>72393</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>792827</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>54213</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>594764</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>90158</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>991290</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>62953</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>693757</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>44859</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>495339</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>35822</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>396063</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>26841</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>296885</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>26532424</v>
+        <v>26043097</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>30496523</v>
+        <v>28890559</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>174116</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>2001003</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>44985</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>494401</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>69785</v>
+        <v>70150</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>769812</v>
+        <v>769320</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>26462639</v>
+        <v>26147063</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>2485955</v>
+        <v>2514037</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>27486425</v>
+        <v>27504296</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>23976684</v>
+        <v>23633026</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>23976684</v>
+        <v>23633026</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>23976684</v>
+        <v>23633026</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>23976684</v>
+        <v>23633026</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>23976684</v>
+        <v>23633026</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
